--- a/rules/terrifs/DVC/03_DVC Tariff Calculation_Jharkand_LT Commercial.xlsx
+++ b/rules/terrifs/DVC/03_DVC Tariff Calculation_Jharkand_LT Commercial.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cuculusindia.sharepoint.com/sites/C003CCIDamodarValleyCorporation/Shared Documents/General/DVC_Tariiff_Calculation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rutusoft\energy-tariff-calculation-engine-service\rules\terrifs\DVC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{04FAE7BC-5614-4425-AF35-C99FFC5F8112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCFE788D-3AF6-4342-A175-924B06857167}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F5C1BD-9616-456E-A245-7B9939D3F3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D0898F0C-93A7-4719-B0FB-F5FD596946B3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D0898F0C-93A7-4719-B0FB-F5FD596946B3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenario 1" sheetId="4" r:id="rId1"/>
-    <sheet name="Scenario 2" sheetId="13" r:id="rId2"/>
-    <sheet name="Scenario 3" sheetId="14" r:id="rId3"/>
+    <sheet name="Scenario 3 (2)" sheetId="17" r:id="rId1"/>
+    <sheet name="Scenario 1" sheetId="4" r:id="rId2"/>
+    <sheet name="Scenario 2" sheetId="13" r:id="rId3"/>
+    <sheet name="Scenario 3" sheetId="14" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -29,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="61">
   <si>
     <t>Scenario 1:</t>
   </si>
@@ -293,7 +292,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -342,6 +341,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -382,7 +387,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -503,6 +508,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -839,6 +847,2272 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC976180-C12A-4618-A2FC-ED8C10C7BDCD}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+  </sheetPr>
+  <dimension ref="A1:S67"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="44.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="19.5546875" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" customWidth="1"/>
+    <col min="16" max="16" width="24.6640625" customWidth="1"/>
+    <col min="17" max="17" width="11.88671875" customWidth="1"/>
+    <col min="18" max="18" width="13.5546875" customWidth="1"/>
+    <col min="19" max="19" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.109375" customWidth="1"/>
+    <col min="22" max="23" width="17.88671875" customWidth="1"/>
+    <col min="24" max="24" width="14.33203125" customWidth="1"/>
+    <col min="25" max="25" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B4" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="25"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B5" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="12">
+        <v>10</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="31">
+        <v>150</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="S7" s="1"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="31">
+        <v>4.3</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="31">
+        <v>0.66</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="34">
+        <v>0.03</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="34">
+        <v>0.06</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="31">
+        <v>1.5</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="44">
+        <v>45870</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="45">
+        <f>DAY(EOMONTH(C13,0))</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B16" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="35">
+        <f>50%*C6</f>
+        <v>5</v>
+      </c>
+      <c r="D17" s="46">
+        <f>C17*$D$24</f>
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="35">
+        <v>10</v>
+      </c>
+      <c r="D18" s="46">
+        <f t="shared" ref="D18:D19" si="0">C18*$D$24</f>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="35">
+        <f>110%*C18</f>
+        <v>11</v>
+      </c>
+      <c r="D19" s="46">
+        <f t="shared" si="0"/>
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B20" s="3"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
+      <c r="P20" s="41"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C22" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="33"/>
+      <c r="E22" s="32"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="27">
+        <v>24</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="27">
+        <v>0.85</v>
+      </c>
+      <c r="J24" s="9"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+    </row>
+    <row r="25" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J25" s="42"/>
+      <c r="K25" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="M25" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="N25" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="O25" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="P25" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q25" s="43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="J26" s="42"/>
+      <c r="K26" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="L26" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="M26" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="N26" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="O26" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="P26" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q26" s="43"/>
+    </row>
+    <row r="27" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J27" s="6"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" s="30">
+        <v>41.5</v>
+      </c>
+      <c r="C28" s="15">
+        <f>C13</f>
+        <v>45870</v>
+      </c>
+      <c r="D28" s="30">
+        <v>45</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="28">
+        <v>1.875</v>
+      </c>
+      <c r="G28" s="16"/>
+      <c r="H28" s="47">
+        <f>IF(F28="", "", MIN($D$18, IF(MAX($F$28:$F$57)&gt;$D$17, MAX($F$28:$F$57), F28)))</f>
+        <v>8.5</v>
+      </c>
+      <c r="J28" s="5">
+        <f>C28</f>
+        <v>45870</v>
+      </c>
+      <c r="K28" s="21">
+        <f>ROUNDUP(H28*($C$7/$C$14),4)</f>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L28" s="21">
+        <f t="shared" ref="L28:L58" si="1">ROUNDUP(D28*$C$8,4)</f>
+        <v>193.5</v>
+      </c>
+      <c r="M28" s="21">
+        <f>A28*$C$9</f>
+        <v>27.39</v>
+      </c>
+      <c r="N28" s="21">
+        <f>ROUNDUP($C$11*(L28+M28),4)</f>
+        <v>13.253399999999999</v>
+      </c>
+      <c r="O28" s="21">
+        <f>ROUNDUP(-L28*$C$10,4)</f>
+        <v>-5.8049999999999997</v>
+      </c>
+      <c r="P28" s="21">
+        <f t="shared" ref="P28:P58" si="2">IF(F28&gt;=$D$19,1.5*$C$7*(F28-$D$18),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="21">
+        <f>ROUNDUP(Q27-(K28+L28+M28+N28+O28+P28),4)</f>
+        <v>-269.46749999999997</v>
+      </c>
+      <c r="R28" s="48">
+        <f>Q28-'Scenario 1'!R28</f>
+        <v>-32.056499999999971</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" s="30">
+        <v>51.5</v>
+      </c>
+      <c r="C29" s="15">
+        <f>C28+1</f>
+        <v>45871</v>
+      </c>
+      <c r="D29" s="30">
+        <v>55</v>
+      </c>
+      <c r="E29" s="16"/>
+      <c r="F29" s="28">
+        <v>2.2916666666666665</v>
+      </c>
+      <c r="G29" s="16"/>
+      <c r="H29" s="47">
+        <f t="shared" ref="H29:H58" si="3">IF(F29="", "", MIN($D$18, IF(MAX($F$28:$F$58)&gt;$D$17, MAX($F$28:$F$58), F29)))</f>
+        <v>8.5</v>
+      </c>
+      <c r="J29" s="5">
+        <f t="shared" ref="J29:J58" si="4">J28+1</f>
+        <v>45871</v>
+      </c>
+      <c r="K29" s="21">
+        <f t="shared" ref="K29:K58" si="5">ROUNDUP(H29*($C$7/$C$14),4)</f>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L29" s="21">
+        <f t="shared" si="1"/>
+        <v>236.5</v>
+      </c>
+      <c r="M29" s="21">
+        <f t="shared" ref="M29:M58" si="6">A29*$C$9</f>
+        <v>33.99</v>
+      </c>
+      <c r="N29" s="21">
+        <f t="shared" ref="N29:N58" si="7">ROUNDUP($C$11*(L29+M29),4)</f>
+        <v>16.229399999999998</v>
+      </c>
+      <c r="O29" s="21">
+        <f t="shared" ref="O29:O58" si="8">ROUNDUP(-L29*$C$10,4)</f>
+        <v>-7.0949999999999998</v>
+      </c>
+      <c r="P29" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="21">
+        <f t="shared" ref="Q29:Q58" si="9">ROUNDUP(Q28-(K29+L29+M29+N29+O29+P29),4)</f>
+        <v>-590.221</v>
+      </c>
+      <c r="R29" s="48">
+        <f>Q29-'Scenario 1'!R29</f>
+        <v>-62.09680000000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30" s="30">
+        <v>68.5</v>
+      </c>
+      <c r="C30" s="15">
+        <f t="shared" ref="C30:C58" si="10">C29+1</f>
+        <v>45872</v>
+      </c>
+      <c r="D30" s="30">
+        <v>72</v>
+      </c>
+      <c r="E30" s="16"/>
+      <c r="F30" s="28">
+        <v>3</v>
+      </c>
+      <c r="G30" s="16"/>
+      <c r="H30" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J30" s="5">
+        <f t="shared" si="4"/>
+        <v>45872</v>
+      </c>
+      <c r="K30" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L30" s="21">
+        <f t="shared" si="1"/>
+        <v>309.60000000000002</v>
+      </c>
+      <c r="M30" s="21">
+        <f t="shared" si="6"/>
+        <v>45.21</v>
+      </c>
+      <c r="N30" s="21">
+        <f t="shared" si="7"/>
+        <v>21.288599999999999</v>
+      </c>
+      <c r="O30" s="21">
+        <f t="shared" si="8"/>
+        <v>-9.2880000000000003</v>
+      </c>
+      <c r="P30" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="21">
+        <f t="shared" si="9"/>
+        <v>-998.16070000000002</v>
+      </c>
+      <c r="R30" s="48">
+        <f>Q30-'Scenario 1'!R30</f>
+        <v>-88.709699999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" s="30">
+        <v>81.5</v>
+      </c>
+      <c r="C31" s="15">
+        <f t="shared" si="10"/>
+        <v>45873</v>
+      </c>
+      <c r="D31" s="30">
+        <v>85</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="F31" s="28">
+        <v>3.5416666666666665</v>
+      </c>
+      <c r="G31" s="16"/>
+      <c r="H31" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J31" s="5">
+        <f t="shared" si="4"/>
+        <v>45873</v>
+      </c>
+      <c r="K31" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L31" s="21">
+        <f t="shared" si="1"/>
+        <v>365.5</v>
+      </c>
+      <c r="M31" s="21">
+        <f t="shared" si="6"/>
+        <v>53.79</v>
+      </c>
+      <c r="N31" s="21">
+        <f t="shared" si="7"/>
+        <v>25.157399999999999</v>
+      </c>
+      <c r="O31" s="21">
+        <f t="shared" si="8"/>
+        <v>-10.965</v>
+      </c>
+      <c r="P31" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="21">
+        <f t="shared" si="9"/>
+        <v>-1472.7722000000001</v>
+      </c>
+      <c r="R31" s="48">
+        <f>Q31-'Scenario 1'!R31</f>
+        <v>-112.70170000000007</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" s="30">
+        <v>61.5</v>
+      </c>
+      <c r="C32" s="15">
+        <f t="shared" si="10"/>
+        <v>45874</v>
+      </c>
+      <c r="D32" s="30">
+        <v>65</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="28">
+        <v>2.7083333333333335</v>
+      </c>
+      <c r="G32" s="16"/>
+      <c r="H32" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J32" s="5">
+        <f>J31+1</f>
+        <v>45874</v>
+      </c>
+      <c r="K32" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L32" s="21">
+        <f t="shared" si="1"/>
+        <v>279.5</v>
+      </c>
+      <c r="M32" s="21">
+        <f t="shared" si="6"/>
+        <v>40.590000000000003</v>
+      </c>
+      <c r="N32" s="21">
+        <f t="shared" si="7"/>
+        <v>19.205400000000001</v>
+      </c>
+      <c r="O32" s="21">
+        <f t="shared" si="8"/>
+        <v>-8.3849999999999998</v>
+      </c>
+      <c r="P32" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="21">
+        <f t="shared" si="9"/>
+        <v>-1844.8117</v>
+      </c>
+      <c r="R32" s="48">
+        <f>Q32-'Scenario 1'!R32</f>
+        <v>-140.72589999999991</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" s="30">
+        <v>78.5</v>
+      </c>
+      <c r="C33" s="15">
+        <f t="shared" si="10"/>
+        <v>45875</v>
+      </c>
+      <c r="D33" s="30">
+        <v>82</v>
+      </c>
+      <c r="E33" s="16"/>
+      <c r="F33" s="47">
+        <v>11.67</v>
+      </c>
+      <c r="G33" s="16"/>
+      <c r="H33" s="47">
+        <v>11.67</v>
+      </c>
+      <c r="J33" s="52">
+        <f t="shared" si="4"/>
+        <v>45875</v>
+      </c>
+      <c r="K33" s="53">
+        <f t="shared" si="5"/>
+        <v>56.467800000000004</v>
+      </c>
+      <c r="L33" s="53">
+        <f t="shared" si="1"/>
+        <v>352.6</v>
+      </c>
+      <c r="M33" s="53">
+        <f t="shared" si="6"/>
+        <v>51.81</v>
+      </c>
+      <c r="N33" s="53">
+        <f t="shared" si="7"/>
+        <v>24.264600000000002</v>
+      </c>
+      <c r="O33" s="53">
+        <f t="shared" si="8"/>
+        <v>-10.577999999999999</v>
+      </c>
+      <c r="P33" s="53">
+        <f t="shared" si="2"/>
+        <v>713.25</v>
+      </c>
+      <c r="Q33" s="53">
+        <f t="shared" si="9"/>
+        <v>-3032.6261</v>
+      </c>
+      <c r="R33" s="54">
+        <f>Q33-'Scenario 1'!R33</f>
+        <v>-893.91139999999996</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" s="30">
+        <v>71.5</v>
+      </c>
+      <c r="C34" s="15">
+        <f t="shared" si="10"/>
+        <v>45876</v>
+      </c>
+      <c r="D34" s="30">
+        <v>75</v>
+      </c>
+      <c r="E34" s="16"/>
+      <c r="F34" s="28">
+        <v>3.125</v>
+      </c>
+      <c r="G34" s="16"/>
+      <c r="H34" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J34" s="5">
+        <f t="shared" si="4"/>
+        <v>45876</v>
+      </c>
+      <c r="K34" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L34" s="21">
+        <f t="shared" si="1"/>
+        <v>322.5</v>
+      </c>
+      <c r="M34" s="21">
+        <f t="shared" si="6"/>
+        <v>47.190000000000005</v>
+      </c>
+      <c r="N34" s="21">
+        <f t="shared" si="7"/>
+        <v>22.1814</v>
+      </c>
+      <c r="O34" s="21">
+        <f t="shared" si="8"/>
+        <v>-9.6750000000000007</v>
+      </c>
+      <c r="P34" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="21">
+        <f t="shared" si="9"/>
+        <v>-3455.9515999999999</v>
+      </c>
+      <c r="R34" s="48">
+        <f>Q34-'Scenario 1'!R34</f>
+        <v>-919.91949999999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A35" s="30">
+        <v>91.5</v>
+      </c>
+      <c r="C35" s="15">
+        <f t="shared" si="10"/>
+        <v>45877</v>
+      </c>
+      <c r="D35" s="30">
+        <v>95</v>
+      </c>
+      <c r="E35" s="16"/>
+      <c r="F35" s="28">
+        <v>3.9583333333333335</v>
+      </c>
+      <c r="G35" s="16"/>
+      <c r="H35" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J35" s="5">
+        <f t="shared" si="4"/>
+        <v>45877</v>
+      </c>
+      <c r="K35" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L35" s="21">
+        <f t="shared" si="1"/>
+        <v>408.5</v>
+      </c>
+      <c r="M35" s="21">
+        <f t="shared" si="6"/>
+        <v>60.39</v>
+      </c>
+      <c r="N35" s="21">
+        <f t="shared" si="7"/>
+        <v>28.133400000000002</v>
+      </c>
+      <c r="O35" s="21">
+        <f t="shared" si="8"/>
+        <v>-12.255000000000001</v>
+      </c>
+      <c r="P35" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="21">
+        <f t="shared" si="9"/>
+        <v>-3981.8490999999999</v>
+      </c>
+      <c r="R35" s="48">
+        <f>Q35-'Scenario 1'!R35</f>
+        <v>-941.89530000000013</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" s="30">
+        <v>84.5</v>
+      </c>
+      <c r="C36" s="15">
+        <f t="shared" si="10"/>
+        <v>45878</v>
+      </c>
+      <c r="D36" s="30">
+        <v>88</v>
+      </c>
+      <c r="E36" s="16"/>
+      <c r="F36" s="28">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="G36" s="16"/>
+      <c r="H36" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J36" s="5">
+        <f t="shared" si="4"/>
+        <v>45878</v>
+      </c>
+      <c r="K36" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L36" s="21">
+        <f t="shared" si="1"/>
+        <v>378.4</v>
+      </c>
+      <c r="M36" s="21">
+        <f t="shared" si="6"/>
+        <v>55.77</v>
+      </c>
+      <c r="N36" s="21">
+        <f t="shared" si="7"/>
+        <v>26.0502</v>
+      </c>
+      <c r="O36" s="21">
+        <f t="shared" si="8"/>
+        <v>-11.352</v>
+      </c>
+      <c r="P36" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="21">
+        <f t="shared" si="9"/>
+        <v>-4471.8464000000004</v>
+      </c>
+      <c r="R36" s="48">
+        <f>Q36-'Scenario 1'!R36</f>
+        <v>-965.28240000000051</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" s="30">
+        <v>93.5</v>
+      </c>
+      <c r="C37" s="15">
+        <f t="shared" si="10"/>
+        <v>45879</v>
+      </c>
+      <c r="D37" s="30">
+        <v>98</v>
+      </c>
+      <c r="E37" s="16"/>
+      <c r="F37" s="28">
+        <v>4.083333333333333</v>
+      </c>
+      <c r="G37" s="16"/>
+      <c r="H37" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J37" s="5">
+        <f t="shared" si="4"/>
+        <v>45879</v>
+      </c>
+      <c r="K37" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L37" s="21">
+        <f t="shared" si="1"/>
+        <v>421.4</v>
+      </c>
+      <c r="M37" s="21">
+        <f t="shared" si="6"/>
+        <v>61.71</v>
+      </c>
+      <c r="N37" s="21">
+        <f t="shared" si="7"/>
+        <v>28.986599999999999</v>
+      </c>
+      <c r="O37" s="21">
+        <f t="shared" si="8"/>
+        <v>-12.641999999999999</v>
+      </c>
+      <c r="P37" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="21">
+        <f t="shared" si="9"/>
+        <v>-5012.4300999999996</v>
+      </c>
+      <c r="R37" s="48">
+        <f>Q37-'Scenario 1'!R37</f>
+        <v>-986.65339999999969</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A38" s="30">
+        <v>90.5</v>
+      </c>
+      <c r="C38" s="15">
+        <f t="shared" si="10"/>
+        <v>45880</v>
+      </c>
+      <c r="D38" s="30">
+        <v>95</v>
+      </c>
+      <c r="E38" s="16"/>
+      <c r="F38" s="28">
+        <v>3.9583333333333335</v>
+      </c>
+      <c r="G38" s="16"/>
+      <c r="H38" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J38" s="5">
+        <f t="shared" si="4"/>
+        <v>45880</v>
+      </c>
+      <c r="K38" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L38" s="21">
+        <f t="shared" si="1"/>
+        <v>408.5</v>
+      </c>
+      <c r="M38" s="21">
+        <f t="shared" si="6"/>
+        <v>59.730000000000004</v>
+      </c>
+      <c r="N38" s="21">
+        <f t="shared" si="7"/>
+        <v>28.093800000000002</v>
+      </c>
+      <c r="O38" s="21">
+        <f t="shared" si="8"/>
+        <v>-12.255000000000001</v>
+      </c>
+      <c r="P38" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="21">
+        <f t="shared" si="9"/>
+        <v>-5537.6279999999997</v>
+      </c>
+      <c r="R38" s="48">
+        <f>Q38-'Scenario 1'!R38</f>
+        <v>-1008.6291999999994</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A39" s="30">
+        <v>70.5</v>
+      </c>
+      <c r="C39" s="15">
+        <f t="shared" si="10"/>
+        <v>45881</v>
+      </c>
+      <c r="D39" s="30">
+        <v>75</v>
+      </c>
+      <c r="E39" s="16"/>
+      <c r="F39" s="28">
+        <v>3.125</v>
+      </c>
+      <c r="G39" s="16"/>
+      <c r="H39" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J39" s="5">
+        <f t="shared" si="4"/>
+        <v>45881</v>
+      </c>
+      <c r="K39" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L39" s="21">
+        <f t="shared" si="1"/>
+        <v>322.5</v>
+      </c>
+      <c r="M39" s="21">
+        <f t="shared" si="6"/>
+        <v>46.53</v>
+      </c>
+      <c r="N39" s="21">
+        <f t="shared" si="7"/>
+        <v>22.1418</v>
+      </c>
+      <c r="O39" s="21">
+        <f t="shared" si="8"/>
+        <v>-9.6750000000000007</v>
+      </c>
+      <c r="P39" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q39" s="21">
+        <f t="shared" si="9"/>
+        <v>-5960.2538999999997</v>
+      </c>
+      <c r="R39" s="48">
+        <f>Q39-'Scenario 1'!R39</f>
+        <v>-1034.6372999999994</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A40" s="30">
+        <v>60.5</v>
+      </c>
+      <c r="C40" s="15">
+        <f t="shared" si="10"/>
+        <v>45882</v>
+      </c>
+      <c r="D40" s="30">
+        <v>65</v>
+      </c>
+      <c r="E40" s="16"/>
+      <c r="F40" s="28">
+        <v>2.7083333333333335</v>
+      </c>
+      <c r="G40" s="16"/>
+      <c r="H40" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J40" s="5">
+        <f t="shared" si="4"/>
+        <v>45882</v>
+      </c>
+      <c r="K40" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L40" s="21">
+        <f t="shared" si="1"/>
+        <v>279.5</v>
+      </c>
+      <c r="M40" s="21">
+        <f t="shared" si="6"/>
+        <v>39.93</v>
+      </c>
+      <c r="N40" s="21">
+        <f t="shared" si="7"/>
+        <v>19.165800000000001</v>
+      </c>
+      <c r="O40" s="21">
+        <f t="shared" si="8"/>
+        <v>-8.3849999999999998</v>
+      </c>
+      <c r="P40" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="21">
+        <f t="shared" si="9"/>
+        <v>-6331.5937999999996</v>
+      </c>
+      <c r="R40" s="48">
+        <f>Q40-'Scenario 1'!R40</f>
+        <v>-1062.6614999999993</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A41" s="30">
+        <v>70.5</v>
+      </c>
+      <c r="C41" s="15">
+        <f t="shared" si="10"/>
+        <v>45883</v>
+      </c>
+      <c r="D41" s="30">
+        <v>75</v>
+      </c>
+      <c r="E41" s="16"/>
+      <c r="F41" s="47">
+        <f>3.125*0+12.856</f>
+        <v>12.856</v>
+      </c>
+      <c r="G41" s="16"/>
+      <c r="H41" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J41" s="5">
+        <f t="shared" si="4"/>
+        <v>45883</v>
+      </c>
+      <c r="K41" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L41" s="21">
+        <f t="shared" si="1"/>
+        <v>322.5</v>
+      </c>
+      <c r="M41" s="21">
+        <f t="shared" si="6"/>
+        <v>46.53</v>
+      </c>
+      <c r="N41" s="21">
+        <f t="shared" si="7"/>
+        <v>22.1418</v>
+      </c>
+      <c r="O41" s="21">
+        <f t="shared" si="8"/>
+        <v>-9.6750000000000007</v>
+      </c>
+      <c r="P41" s="21">
+        <f t="shared" si="2"/>
+        <v>980.1</v>
+      </c>
+      <c r="Q41" s="21">
+        <f t="shared" si="9"/>
+        <v>-7734.3197</v>
+      </c>
+      <c r="R41" s="48">
+        <f>Q41-'Scenario 1'!R41</f>
+        <v>-2068.7695999999996</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A42" s="30">
+        <v>90.5</v>
+      </c>
+      <c r="C42" s="15">
+        <f t="shared" si="10"/>
+        <v>45884</v>
+      </c>
+      <c r="D42" s="30">
+        <v>95</v>
+      </c>
+      <c r="E42" s="16"/>
+      <c r="F42" s="28">
+        <v>3.9583333333333335</v>
+      </c>
+      <c r="G42" s="16"/>
+      <c r="H42" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J42" s="5">
+        <f t="shared" si="4"/>
+        <v>45884</v>
+      </c>
+      <c r="K42" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L42" s="21">
+        <f t="shared" si="1"/>
+        <v>408.5</v>
+      </c>
+      <c r="M42" s="21">
+        <f t="shared" si="6"/>
+        <v>59.730000000000004</v>
+      </c>
+      <c r="N42" s="21">
+        <f t="shared" si="7"/>
+        <v>28.093800000000002</v>
+      </c>
+      <c r="O42" s="21">
+        <f t="shared" si="8"/>
+        <v>-12.255000000000001</v>
+      </c>
+      <c r="P42" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q42" s="21">
+        <f t="shared" si="9"/>
+        <v>-8259.5175999999992</v>
+      </c>
+      <c r="R42" s="48">
+        <f>Q42-'Scenario 1'!R42</f>
+        <v>-2090.7453999999989</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A43" s="30">
+        <v>80.5</v>
+      </c>
+      <c r="C43" s="15">
+        <f t="shared" si="10"/>
+        <v>45885</v>
+      </c>
+      <c r="D43" s="30">
+        <v>85</v>
+      </c>
+      <c r="E43" s="16"/>
+      <c r="F43" s="28">
+        <v>3.5416666666666665</v>
+      </c>
+      <c r="G43" s="16"/>
+      <c r="H43" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J43" s="5">
+        <f t="shared" si="4"/>
+        <v>45885</v>
+      </c>
+      <c r="K43" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L43" s="21">
+        <f t="shared" si="1"/>
+        <v>365.5</v>
+      </c>
+      <c r="M43" s="21">
+        <f t="shared" si="6"/>
+        <v>53.13</v>
+      </c>
+      <c r="N43" s="21">
+        <f t="shared" si="7"/>
+        <v>25.117799999999999</v>
+      </c>
+      <c r="O43" s="21">
+        <f t="shared" si="8"/>
+        <v>-10.965</v>
+      </c>
+      <c r="P43" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q43" s="21">
+        <f t="shared" si="9"/>
+        <v>-8733.4295000000002</v>
+      </c>
+      <c r="R43" s="48">
+        <f>Q43-'Scenario 1'!R43</f>
+        <v>-2114.7374</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A44" s="30">
+        <v>83.5</v>
+      </c>
+      <c r="C44" s="15">
+        <f t="shared" si="10"/>
+        <v>45886</v>
+      </c>
+      <c r="D44" s="30">
+        <v>88</v>
+      </c>
+      <c r="E44" s="16"/>
+      <c r="F44" s="28">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="G44" s="16"/>
+      <c r="H44" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J44" s="5">
+        <f t="shared" si="4"/>
+        <v>45886</v>
+      </c>
+      <c r="K44" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L44" s="21">
+        <f t="shared" si="1"/>
+        <v>378.4</v>
+      </c>
+      <c r="M44" s="21">
+        <f t="shared" si="6"/>
+        <v>55.11</v>
+      </c>
+      <c r="N44" s="21">
+        <f t="shared" si="7"/>
+        <v>26.0106</v>
+      </c>
+      <c r="O44" s="21">
+        <f t="shared" si="8"/>
+        <v>-11.352</v>
+      </c>
+      <c r="P44" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q44" s="21">
+        <f t="shared" si="9"/>
+        <v>-9222.7271999999994</v>
+      </c>
+      <c r="R44" s="48">
+        <f>Q44-'Scenario 1'!R44</f>
+        <v>-2138.124499999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A45" s="30">
+        <v>93.5</v>
+      </c>
+      <c r="C45" s="15">
+        <f t="shared" si="10"/>
+        <v>45887</v>
+      </c>
+      <c r="D45" s="30">
+        <v>98</v>
+      </c>
+      <c r="E45" s="16"/>
+      <c r="F45" s="28">
+        <v>4.083333333333333</v>
+      </c>
+      <c r="G45" s="16"/>
+      <c r="H45" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J45" s="5">
+        <f t="shared" si="4"/>
+        <v>45887</v>
+      </c>
+      <c r="K45" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L45" s="21">
+        <f t="shared" si="1"/>
+        <v>421.4</v>
+      </c>
+      <c r="M45" s="21">
+        <f t="shared" si="6"/>
+        <v>61.71</v>
+      </c>
+      <c r="N45" s="21">
+        <f t="shared" si="7"/>
+        <v>28.986599999999999</v>
+      </c>
+      <c r="O45" s="21">
+        <f t="shared" si="8"/>
+        <v>-12.641999999999999</v>
+      </c>
+      <c r="P45" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q45" s="21">
+        <f t="shared" si="9"/>
+        <v>-9763.3109000000004</v>
+      </c>
+      <c r="R45" s="48">
+        <f>Q45-'Scenario 1'!R45</f>
+        <v>-2159.4955</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A46" s="30">
+        <v>90.5</v>
+      </c>
+      <c r="C46" s="15">
+        <f t="shared" si="10"/>
+        <v>45888</v>
+      </c>
+      <c r="D46" s="30">
+        <v>95</v>
+      </c>
+      <c r="E46" s="16"/>
+      <c r="F46" s="28">
+        <v>4.25</v>
+      </c>
+      <c r="G46" s="16"/>
+      <c r="H46" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J46" s="5">
+        <f t="shared" si="4"/>
+        <v>45888</v>
+      </c>
+      <c r="K46" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L46" s="21">
+        <f t="shared" si="1"/>
+        <v>408.5</v>
+      </c>
+      <c r="M46" s="21">
+        <f t="shared" si="6"/>
+        <v>59.730000000000004</v>
+      </c>
+      <c r="N46" s="21">
+        <f t="shared" si="7"/>
+        <v>28.093800000000002</v>
+      </c>
+      <c r="O46" s="21">
+        <f t="shared" si="8"/>
+        <v>-12.255000000000001</v>
+      </c>
+      <c r="P46" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="21">
+        <f t="shared" si="9"/>
+        <v>-10288.5088</v>
+      </c>
+      <c r="R46" s="48">
+        <f>Q46-'Scenario 1'!R46</f>
+        <v>-2180.0599999999995</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A47" s="30">
+        <v>93.5</v>
+      </c>
+      <c r="C47" s="15">
+        <f t="shared" si="10"/>
+        <v>45889</v>
+      </c>
+      <c r="D47" s="30">
+        <v>98</v>
+      </c>
+      <c r="E47" s="16"/>
+      <c r="F47" s="28">
+        <v>4.083333333333333</v>
+      </c>
+      <c r="G47" s="16"/>
+      <c r="H47" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J47" s="5">
+        <f t="shared" si="4"/>
+        <v>45889</v>
+      </c>
+      <c r="K47" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L47" s="21">
+        <f t="shared" si="1"/>
+        <v>421.4</v>
+      </c>
+      <c r="M47" s="21">
+        <f t="shared" si="6"/>
+        <v>61.71</v>
+      </c>
+      <c r="N47" s="21">
+        <f t="shared" si="7"/>
+        <v>28.986599999999999</v>
+      </c>
+      <c r="O47" s="21">
+        <f t="shared" si="8"/>
+        <v>-12.641999999999999</v>
+      </c>
+      <c r="P47" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q47" s="21">
+        <f t="shared" si="9"/>
+        <v>-10829.092500000001</v>
+      </c>
+      <c r="R47" s="48">
+        <f>Q47-'Scenario 1'!R47</f>
+        <v>-2201.4310000000005</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A48" s="30">
+        <v>83.5</v>
+      </c>
+      <c r="C48" s="15">
+        <f t="shared" si="10"/>
+        <v>45890</v>
+      </c>
+      <c r="D48" s="30">
+        <v>88</v>
+      </c>
+      <c r="E48" s="16"/>
+      <c r="F48" s="28">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="G48" s="16"/>
+      <c r="H48" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J48" s="5">
+        <f t="shared" si="4"/>
+        <v>45890</v>
+      </c>
+      <c r="K48" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L48" s="21">
+        <f t="shared" si="1"/>
+        <v>378.4</v>
+      </c>
+      <c r="M48" s="21">
+        <f t="shared" si="6"/>
+        <v>55.11</v>
+      </c>
+      <c r="N48" s="21">
+        <f t="shared" si="7"/>
+        <v>26.0106</v>
+      </c>
+      <c r="O48" s="21">
+        <f t="shared" si="8"/>
+        <v>-11.352</v>
+      </c>
+      <c r="P48" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="21">
+        <f t="shared" si="9"/>
+        <v>-11318.3902</v>
+      </c>
+      <c r="R48" s="48">
+        <f>Q48-'Scenario 1'!R48</f>
+        <v>-2224.8181000000004</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A49" s="30">
+        <v>75.5</v>
+      </c>
+      <c r="C49" s="15">
+        <f t="shared" si="10"/>
+        <v>45891</v>
+      </c>
+      <c r="D49" s="30">
+        <v>78</v>
+      </c>
+      <c r="E49" s="16"/>
+      <c r="F49" s="28">
+        <v>3.25</v>
+      </c>
+      <c r="G49" s="16"/>
+      <c r="H49" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J49" s="5">
+        <f t="shared" si="4"/>
+        <v>45891</v>
+      </c>
+      <c r="K49" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L49" s="21">
+        <f t="shared" si="1"/>
+        <v>335.4</v>
+      </c>
+      <c r="M49" s="21">
+        <f t="shared" si="6"/>
+        <v>49.830000000000005</v>
+      </c>
+      <c r="N49" s="21">
+        <f t="shared" si="7"/>
+        <v>23.113800000000001</v>
+      </c>
+      <c r="O49" s="21">
+        <f t="shared" si="8"/>
+        <v>-10.061999999999999</v>
+      </c>
+      <c r="P49" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="21">
+        <f t="shared" si="9"/>
+        <v>-11757.801100000001</v>
+      </c>
+      <c r="R49" s="48">
+        <f>Q49-'Scenario 1'!R49</f>
+        <v>-2250.2213000000011</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A50" s="30">
+        <v>87.5</v>
+      </c>
+      <c r="C50" s="15">
+        <f t="shared" si="10"/>
+        <v>45892</v>
+      </c>
+      <c r="D50" s="30">
+        <v>90</v>
+      </c>
+      <c r="E50" s="16"/>
+      <c r="F50" s="28">
+        <v>3.75</v>
+      </c>
+      <c r="G50" s="16"/>
+      <c r="H50" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J50" s="5">
+        <f t="shared" si="4"/>
+        <v>45892</v>
+      </c>
+      <c r="K50" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L50" s="21">
+        <f t="shared" si="1"/>
+        <v>387</v>
+      </c>
+      <c r="M50" s="21">
+        <f t="shared" si="6"/>
+        <v>57.75</v>
+      </c>
+      <c r="N50" s="21">
+        <f t="shared" si="7"/>
+        <v>26.684999999999999</v>
+      </c>
+      <c r="O50" s="21">
+        <f t="shared" si="8"/>
+        <v>-11.61</v>
+      </c>
+      <c r="P50" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q50" s="21">
+        <f t="shared" si="9"/>
+        <v>-12258.7552</v>
+      </c>
+      <c r="R50" s="48">
+        <f>Q50-'Scenario 1'!R50</f>
+        <v>-2273.2052000000003</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A51" s="30">
+        <v>87.5</v>
+      </c>
+      <c r="C51" s="15">
+        <f t="shared" si="10"/>
+        <v>45893</v>
+      </c>
+      <c r="D51" s="30">
+        <v>90</v>
+      </c>
+      <c r="E51" s="16"/>
+      <c r="F51" s="28">
+        <v>3.75</v>
+      </c>
+      <c r="G51" s="16"/>
+      <c r="H51" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J51" s="5">
+        <f t="shared" si="4"/>
+        <v>45893</v>
+      </c>
+      <c r="K51" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L51" s="21">
+        <f t="shared" si="1"/>
+        <v>387</v>
+      </c>
+      <c r="M51" s="21">
+        <f t="shared" si="6"/>
+        <v>57.75</v>
+      </c>
+      <c r="N51" s="21">
+        <f t="shared" si="7"/>
+        <v>26.684999999999999</v>
+      </c>
+      <c r="O51" s="21">
+        <f t="shared" si="8"/>
+        <v>-11.61</v>
+      </c>
+      <c r="P51" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q51" s="21">
+        <f t="shared" si="9"/>
+        <v>-12759.7093</v>
+      </c>
+      <c r="R51" s="48">
+        <f>Q51-'Scenario 1'!R51</f>
+        <v>-2296.1890999999996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A52" s="30">
+        <v>85.5</v>
+      </c>
+      <c r="C52" s="15">
+        <f t="shared" si="10"/>
+        <v>45894</v>
+      </c>
+      <c r="D52" s="30">
+        <v>88</v>
+      </c>
+      <c r="E52" s="16"/>
+      <c r="F52" s="28">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="G52" s="16"/>
+      <c r="H52" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J52" s="5">
+        <f t="shared" si="4"/>
+        <v>45894</v>
+      </c>
+      <c r="K52" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L52" s="21">
+        <f t="shared" si="1"/>
+        <v>378.4</v>
+      </c>
+      <c r="M52" s="21">
+        <f t="shared" si="6"/>
+        <v>56.43</v>
+      </c>
+      <c r="N52" s="21">
+        <f t="shared" si="7"/>
+        <v>26.0898</v>
+      </c>
+      <c r="O52" s="21">
+        <f t="shared" si="8"/>
+        <v>-11.352</v>
+      </c>
+      <c r="P52" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q52" s="21">
+        <f t="shared" si="9"/>
+        <v>-13250.406199999999</v>
+      </c>
+      <c r="R52" s="48">
+        <f>Q52-'Scenario 1'!R52</f>
+        <v>-2319.5761999999995</v>
+      </c>
+      <c r="S52" s="48"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A53" s="30">
+        <v>92.5</v>
+      </c>
+      <c r="C53" s="15">
+        <f t="shared" si="10"/>
+        <v>45895</v>
+      </c>
+      <c r="D53" s="30">
+        <v>95</v>
+      </c>
+      <c r="E53" s="16"/>
+      <c r="F53" s="28">
+        <v>3.9583333333333335</v>
+      </c>
+      <c r="G53" s="16"/>
+      <c r="H53" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J53" s="5">
+        <f t="shared" si="4"/>
+        <v>45895</v>
+      </c>
+      <c r="K53" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L53" s="21">
+        <f t="shared" si="1"/>
+        <v>408.5</v>
+      </c>
+      <c r="M53" s="21">
+        <f t="shared" si="6"/>
+        <v>61.050000000000004</v>
+      </c>
+      <c r="N53" s="21">
+        <f t="shared" si="7"/>
+        <v>28.172999999999998</v>
+      </c>
+      <c r="O53" s="21">
+        <f t="shared" si="8"/>
+        <v>-12.255000000000001</v>
+      </c>
+      <c r="P53" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q53" s="21">
+        <f t="shared" si="9"/>
+        <v>-13777.0033</v>
+      </c>
+      <c r="R53" s="48">
+        <f>Q53-'Scenario 1'!R53</f>
+        <v>-2341.5519999999997</v>
+      </c>
+      <c r="S53" s="48"/>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A54" s="30">
+        <v>95.5</v>
+      </c>
+      <c r="C54" s="15">
+        <f t="shared" si="10"/>
+        <v>45896</v>
+      </c>
+      <c r="D54" s="30">
+        <v>98</v>
+      </c>
+      <c r="E54" s="16"/>
+      <c r="F54" s="28">
+        <v>4.083333333333333</v>
+      </c>
+      <c r="G54" s="16"/>
+      <c r="H54" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J54" s="5">
+        <f t="shared" si="4"/>
+        <v>45896</v>
+      </c>
+      <c r="K54" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L54" s="21">
+        <f t="shared" si="1"/>
+        <v>421.4</v>
+      </c>
+      <c r="M54" s="21">
+        <f t="shared" si="6"/>
+        <v>63.03</v>
+      </c>
+      <c r="N54" s="21">
+        <f t="shared" si="7"/>
+        <v>29.065799999999999</v>
+      </c>
+      <c r="O54" s="21">
+        <f t="shared" si="8"/>
+        <v>-12.641999999999999</v>
+      </c>
+      <c r="P54" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q54" s="21">
+        <f t="shared" si="9"/>
+        <v>-14318.986199999999</v>
+      </c>
+      <c r="R54" s="48">
+        <f>Q54-'Scenario 1'!R54</f>
+        <v>-2362.9229999999989</v>
+      </c>
+      <c r="S54" s="48"/>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A55" s="30">
+        <v>98.5</v>
+      </c>
+      <c r="C55" s="15">
+        <f t="shared" si="10"/>
+        <v>45897</v>
+      </c>
+      <c r="D55" s="30">
+        <v>101</v>
+      </c>
+      <c r="E55" s="16"/>
+      <c r="F55" s="28">
+        <v>4.208333333333333</v>
+      </c>
+      <c r="G55" s="16"/>
+      <c r="H55" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J55" s="5">
+        <f t="shared" si="4"/>
+        <v>45897</v>
+      </c>
+      <c r="K55" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L55" s="21">
+        <f t="shared" si="1"/>
+        <v>434.3</v>
+      </c>
+      <c r="M55" s="21">
+        <f t="shared" si="6"/>
+        <v>65.010000000000005</v>
+      </c>
+      <c r="N55" s="21">
+        <f t="shared" si="7"/>
+        <v>29.958600000000001</v>
+      </c>
+      <c r="O55" s="21">
+        <f t="shared" si="8"/>
+        <v>-13.029</v>
+      </c>
+      <c r="P55" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q55" s="21">
+        <f t="shared" si="9"/>
+        <v>-14876.3549</v>
+      </c>
+      <c r="R55" s="48">
+        <f>Q55-'Scenario 1'!R55</f>
+        <v>-2383.6890999999996</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A56" s="30">
+        <v>85.5</v>
+      </c>
+      <c r="C56" s="15">
+        <f t="shared" si="10"/>
+        <v>45898</v>
+      </c>
+      <c r="D56" s="30">
+        <v>88</v>
+      </c>
+      <c r="E56" s="16"/>
+      <c r="F56" s="28">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="G56" s="16"/>
+      <c r="H56" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J56" s="5">
+        <f t="shared" si="4"/>
+        <v>45898</v>
+      </c>
+      <c r="K56" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L56" s="21">
+        <f t="shared" si="1"/>
+        <v>378.4</v>
+      </c>
+      <c r="M56" s="21">
+        <f t="shared" si="6"/>
+        <v>56.43</v>
+      </c>
+      <c r="N56" s="21">
+        <f t="shared" si="7"/>
+        <v>26.0898</v>
+      </c>
+      <c r="O56" s="21">
+        <f t="shared" si="8"/>
+        <v>-11.352</v>
+      </c>
+      <c r="P56" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q56" s="21">
+        <f t="shared" si="9"/>
+        <v>-15367.051799999999</v>
+      </c>
+      <c r="R56" s="48">
+        <f>Q56-'Scenario 1'!R56</f>
+        <v>-2407.0761999999995</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A57" s="30">
+        <v>92.5</v>
+      </c>
+      <c r="C57" s="15">
+        <f t="shared" si="10"/>
+        <v>45899</v>
+      </c>
+      <c r="D57" s="30">
+        <v>95</v>
+      </c>
+      <c r="E57" s="16"/>
+      <c r="F57" s="28">
+        <v>3.9583333333333335</v>
+      </c>
+      <c r="G57" s="16"/>
+      <c r="H57" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J57" s="5">
+        <f t="shared" si="4"/>
+        <v>45899</v>
+      </c>
+      <c r="K57" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L57" s="21">
+        <f t="shared" si="1"/>
+        <v>408.5</v>
+      </c>
+      <c r="M57" s="21">
+        <f t="shared" si="6"/>
+        <v>61.050000000000004</v>
+      </c>
+      <c r="N57" s="21">
+        <f t="shared" si="7"/>
+        <v>28.172999999999998</v>
+      </c>
+      <c r="O57" s="21">
+        <f t="shared" si="8"/>
+        <v>-12.255000000000001</v>
+      </c>
+      <c r="P57" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="21">
+        <f t="shared" si="9"/>
+        <v>-15893.6489</v>
+      </c>
+      <c r="R57" s="48">
+        <f>Q57-'Scenario 1'!R57</f>
+        <v>-2429.0519999999997</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A58" s="30">
+        <v>92.5</v>
+      </c>
+      <c r="C58" s="15">
+        <f t="shared" si="10"/>
+        <v>45900</v>
+      </c>
+      <c r="D58" s="30">
+        <v>95</v>
+      </c>
+      <c r="E58" s="16"/>
+      <c r="F58" s="28">
+        <v>3.9583333333333335</v>
+      </c>
+      <c r="G58" s="16"/>
+      <c r="H58" s="47">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="J58" s="5">
+        <f t="shared" si="4"/>
+        <v>45900</v>
+      </c>
+      <c r="K58" s="21">
+        <f t="shared" si="5"/>
+        <v>41.129100000000001</v>
+      </c>
+      <c r="L58" s="21">
+        <f t="shared" si="1"/>
+        <v>408.5</v>
+      </c>
+      <c r="M58" s="21">
+        <f t="shared" si="6"/>
+        <v>61.050000000000004</v>
+      </c>
+      <c r="N58" s="21">
+        <f t="shared" si="7"/>
+        <v>28.172999999999998</v>
+      </c>
+      <c r="O58" s="21">
+        <f t="shared" si="8"/>
+        <v>-12.255000000000001</v>
+      </c>
+      <c r="P58" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="21">
+        <f t="shared" si="9"/>
+        <v>-16420.245999999999</v>
+      </c>
+      <c r="R58" s="48">
+        <f>Q58-'Scenario 1'!R58</f>
+        <v>-2451.0277999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J59" s="5"/>
+      <c r="K59" s="21"/>
+      <c r="L59" s="21"/>
+      <c r="M59" s="21"/>
+      <c r="N59" s="21"/>
+      <c r="O59" s="21"/>
+      <c r="P59" s="21"/>
+      <c r="Q59" s="21"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="E60" s="17"/>
+      <c r="K60" s="21"/>
+      <c r="L60" s="21"/>
+      <c r="M60" s="21"/>
+      <c r="N60" s="21"/>
+      <c r="O60" s="21"/>
+      <c r="P60" s="21"/>
+      <c r="Q60" s="21"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J61" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="K61" s="21"/>
+      <c r="L61" s="21">
+        <f>SUM(K28:K59)</f>
+        <v>1290.3408000000006</v>
+      </c>
+      <c r="M61" s="21"/>
+      <c r="N61" s="21"/>
+      <c r="O61" s="21"/>
+      <c r="P61" s="21"/>
+      <c r="Q61" s="21"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J62" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="K62" s="21"/>
+      <c r="L62" s="21">
+        <f>SUM(L28:L59)</f>
+        <v>11330.499999999996</v>
+      </c>
+      <c r="M62" s="21"/>
+      <c r="N62" s="21"/>
+      <c r="O62" s="21"/>
+      <c r="P62" s="21"/>
+      <c r="Q62" s="21"/>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J63" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="K63" s="21"/>
+      <c r="L63" s="21">
+        <f>SUM(M28:M59)</f>
+        <v>1666.1699999999998</v>
+      </c>
+      <c r="M63" s="21"/>
+      <c r="N63" s="21"/>
+      <c r="O63" s="21"/>
+      <c r="P63" s="21"/>
+      <c r="Q63" s="21"/>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J64" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="K64" s="21"/>
+      <c r="L64" s="21">
+        <f>SUM(N28:N59)</f>
+        <v>779.80019999999979</v>
+      </c>
+      <c r="M64" s="21"/>
+      <c r="N64" s="21"/>
+      <c r="O64" s="21"/>
+      <c r="P64" s="21"/>
+      <c r="Q64" s="21"/>
+    </row>
+    <row r="65" spans="10:17" x14ac:dyDescent="0.3">
+      <c r="J65" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="K65" s="21"/>
+      <c r="L65" s="21">
+        <f>SUM(O28:O59)</f>
+        <v>-339.91499999999996</v>
+      </c>
+      <c r="M65" s="21"/>
+      <c r="N65" s="21"/>
+      <c r="O65" s="21"/>
+      <c r="P65" s="21"/>
+      <c r="Q65" s="21"/>
+    </row>
+    <row r="66" spans="10:17" x14ac:dyDescent="0.3">
+      <c r="J66" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K66" s="29"/>
+      <c r="L66" s="29">
+        <f>SUM(P28:P59)</f>
+        <v>1693.35</v>
+      </c>
+      <c r="M66" s="21"/>
+      <c r="N66" s="21"/>
+      <c r="O66" s="21"/>
+      <c r="P66" s="21"/>
+      <c r="Q66" s="21"/>
+    </row>
+    <row r="67" spans="10:17" x14ac:dyDescent="0.3">
+      <c r="J67" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="K67" s="21"/>
+      <c r="L67" s="22">
+        <f>SUM(L61:L66)</f>
+        <v>16420.245999999996</v>
+      </c>
+      <c r="M67" s="21"/>
+      <c r="N67" s="21"/>
+      <c r="O67" s="21"/>
+      <c r="P67" s="21"/>
+      <c r="Q67" s="21"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F8AB3F1-A601-4B70-8C88-E22DF66FCF65}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -2976,7 +5250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFA76450-E92A-4885-9800-4A6E793CF9AE}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -5135,7 +7409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0D25DA-9A30-40E4-A127-2E2BA2C02FFE}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
@@ -5785,7 +8059,7 @@
         <v>-140.72589999999991</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="30">
         <v>78.5</v>
       </c>
@@ -5837,8 +8111,12 @@
         <f t="shared" si="9"/>
         <v>-3017.2874000000002</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R33" s="48">
+        <f>Q33-'Scenario 1'!R33</f>
+        <v>-878.57270000000017</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="30">
         <v>71.5</v>
       </c>
@@ -5890,8 +8168,12 @@
         <f t="shared" si="9"/>
         <v>-3440.6129000000001</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R34" s="48">
+        <f>Q34-'Scenario 1'!R34</f>
+        <v>-904.58080000000018</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="30">
         <v>91.5</v>
       </c>
@@ -5943,8 +8225,12 @@
         <f t="shared" si="9"/>
         <v>-3966.5104000000001</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R35" s="48">
+        <f>Q35-'Scenario 1'!R35</f>
+        <v>-926.55660000000034</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="30">
         <v>84.5</v>
       </c>
@@ -5996,8 +8282,12 @@
         <f t="shared" si="9"/>
         <v>-4456.5077000000001</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R36" s="48">
+        <f>Q36-'Scenario 1'!R36</f>
+        <v>-949.94370000000026</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="30">
         <v>93.5</v>
       </c>
@@ -6049,8 +8339,12 @@
         <f t="shared" si="9"/>
         <v>-4997.0914000000002</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R37" s="48">
+        <f>Q37-'Scenario 1'!R37</f>
+        <v>-971.31470000000036</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="30">
         <v>90.5</v>
       </c>
@@ -6102,8 +8396,12 @@
         <f t="shared" si="9"/>
         <v>-5522.2893000000004</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R38" s="48">
+        <f>Q38-'Scenario 1'!R38</f>
+        <v>-993.29050000000007</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="30">
         <v>70.5</v>
       </c>
@@ -6155,8 +8453,12 @@
         <f t="shared" si="9"/>
         <v>-5944.9152000000004</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R39" s="48">
+        <f>Q39-'Scenario 1'!R39</f>
+        <v>-1019.2986000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="30">
         <v>60.5</v>
       </c>
@@ -6208,8 +8510,12 @@
         <f t="shared" si="9"/>
         <v>-6316.2551000000003</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R40" s="48">
+        <f>Q40-'Scenario 1'!R40</f>
+        <v>-1047.3227999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="30">
         <v>70.5</v>
       </c>
@@ -6262,8 +8568,12 @@
         <f t="shared" si="9"/>
         <v>-7718.9809999999998</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R41" s="48">
+        <f>Q41-'Scenario 1'!R41</f>
+        <v>-2053.4308999999994</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="30">
         <v>90.5</v>
       </c>
@@ -6315,8 +8625,12 @@
         <f t="shared" si="9"/>
         <v>-8244.1789000000008</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R42" s="48">
+        <f>Q42-'Scenario 1'!R42</f>
+        <v>-2075.4067000000005</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="30">
         <v>80.5</v>
       </c>
@@ -6368,8 +8682,12 @@
         <f t="shared" si="9"/>
         <v>-8718.0907999999999</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R43" s="48">
+        <f>Q43-'Scenario 1'!R43</f>
+        <v>-2099.3986999999997</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="30">
         <v>83.5</v>
       </c>
@@ -6421,8 +8739,12 @@
         <f t="shared" si="9"/>
         <v>-9207.3884999999991</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R44" s="48">
+        <f>Q44-'Scenario 1'!R44</f>
+        <v>-2122.7857999999987</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="30">
         <v>93.5</v>
       </c>
@@ -6474,8 +8796,12 @@
         <f t="shared" si="9"/>
         <v>-9747.9722000000002</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R45" s="48">
+        <f>Q45-'Scenario 1'!R45</f>
+        <v>-2144.1567999999997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="30">
         <v>90.5</v>
       </c>
@@ -6527,8 +8853,12 @@
         <f t="shared" si="9"/>
         <v>-10273.170099999999</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R46" s="48">
+        <f>Q46-'Scenario 1'!R46</f>
+        <v>-2164.7212999999992</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="30">
         <v>93.5</v>
       </c>
@@ -6580,8 +8910,12 @@
         <f t="shared" si="9"/>
         <v>-10813.7538</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R47" s="48">
+        <f>Q47-'Scenario 1'!R47</f>
+        <v>-2186.0923000000003</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="30">
         <v>83.5</v>
       </c>
@@ -6633,6 +8967,10 @@
         <f t="shared" si="9"/>
         <v>-11303.0515</v>
       </c>
+      <c r="R48" s="48">
+        <f>Q48-'Scenario 1'!R48</f>
+        <v>-2209.4794000000002</v>
+      </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="30">
@@ -6686,6 +9024,10 @@
         <f t="shared" si="9"/>
         <v>-11742.4624</v>
       </c>
+      <c r="R49" s="48">
+        <f>Q49-'Scenario 1'!R49</f>
+        <v>-2234.8826000000008</v>
+      </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="30">
@@ -6739,6 +9081,10 @@
         <f t="shared" si="9"/>
         <v>-12243.416499999999</v>
       </c>
+      <c r="R50" s="48">
+        <f>Q50-'Scenario 1'!R50</f>
+        <v>-2257.8665000000001</v>
+      </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="30">
@@ -6792,6 +9138,10 @@
         <f t="shared" si="9"/>
         <v>-12744.3706</v>
       </c>
+      <c r="R51" s="48">
+        <f>Q51-'Scenario 1'!R51</f>
+        <v>-2280.8503999999994</v>
+      </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="30">
@@ -6845,6 +9195,10 @@
         <f t="shared" si="9"/>
         <v>-13235.067499999999</v>
       </c>
+      <c r="R52" s="48">
+        <f>Q52-'Scenario 1'!R52</f>
+        <v>-2304.2374999999993</v>
+      </c>
       <c r="S52" s="48"/>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
@@ -6899,6 +9253,10 @@
         <f t="shared" si="9"/>
         <v>-13761.6646</v>
       </c>
+      <c r="R53" s="48">
+        <f>Q53-'Scenario 1'!R53</f>
+        <v>-2326.2132999999994</v>
+      </c>
       <c r="S53" s="48"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
@@ -6953,6 +9311,10 @@
         <f t="shared" si="9"/>
         <v>-14303.647499999999</v>
       </c>
+      <c r="R54" s="48">
+        <f>Q54-'Scenario 1'!R54</f>
+        <v>-2347.5842999999986</v>
+      </c>
       <c r="S54" s="48"/>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
@@ -7007,6 +9369,10 @@
         <f t="shared" si="9"/>
         <v>-14861.0162</v>
       </c>
+      <c r="R55" s="48">
+        <f>Q55-'Scenario 1'!R55</f>
+        <v>-2368.3503999999994</v>
+      </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="30">
@@ -7060,6 +9426,10 @@
         <f t="shared" si="9"/>
         <v>-15351.713100000001</v>
       </c>
+      <c r="R56" s="48">
+        <f>Q56-'Scenario 1'!R56</f>
+        <v>-2391.7375000000011</v>
+      </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="30">
@@ -7113,6 +9483,10 @@
         <f t="shared" si="9"/>
         <v>-15878.3102</v>
       </c>
+      <c r="R57" s="48">
+        <f>Q57-'Scenario 1'!R57</f>
+        <v>-2413.7132999999994</v>
+      </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="30">
@@ -7165,6 +9539,10 @@
       <c r="Q58" s="21">
         <f t="shared" si="9"/>
         <v>-16404.907299999999</v>
+      </c>
+      <c r="R58" s="48">
+        <f>Q58-'Scenario 1'!R58</f>
+        <v>-2435.6890999999996</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.3">
@@ -7299,26 +9677,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f7782821-aae6-4082-a5ba-ea6cec871eae">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8ae689fd-2d0a-4368-81dd-a81ec3a4c1cb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100289DECD7A7FC114684EE8459FBE95C46" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d54900b6250314b6ca1928107e1e097">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f7782821-aae6-4082-a5ba-ea6cec871eae" xmlns:ns3="8ae689fd-2d0a-4368-81dd-a81ec3a4c1cb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90f563c9498c1415a0ecb9517f538d29" ns2:_="" ns3:_="">
     <xsd:import namespace="f7782821-aae6-4082-a5ba-ea6cec871eae"/>
@@ -7513,10 +9871,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f7782821-aae6-4082-a5ba-ea6cec871eae">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8ae689fd-2d0a-4368-81dd-a81ec3a4c1cb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{225BDEBB-EC5F-4272-9192-54C1651D3797}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E89D01C-46A6-4941-9CCD-519DF33CCA1C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f7782821-aae6-4082-a5ba-ea6cec871eae"/>
+    <ds:schemaRef ds:uri="8ae689fd-2d0a-4368-81dd-a81ec3a4c1cb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7533,5 +9922,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E89D01C-46A6-4941-9CCD-519DF33CCA1C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{225BDEBB-EC5F-4272-9192-54C1651D3797}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>